--- a/data/processed/ethiopia_fi_unified_data_updated.xlsx
+++ b/data/processed/ethiopia_fi_unified_data_updated.xlsx
@@ -638,13 +638,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L2" s="1" t="n">
-        <v>42004</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2014-12-31</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>2014</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -689,8 +693,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE2" s="1" t="n">
-        <v>45677</v>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
@@ -746,13 +752,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L3" s="1" t="n">
-        <v>43100</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2017-12-31</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>2017</v>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -797,8 +807,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE3" s="1" t="n">
-        <v>45677</v>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -850,13 +862,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L4" s="1" t="n">
-        <v>44561</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>2021</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -901,8 +917,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE4" s="1" t="n">
-        <v>45677</v>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
@@ -954,13 +972,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L5" s="1" t="n">
-        <v>44561</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>2021</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1005,8 +1027,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE5" s="1" t="n">
-        <v>45677</v>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
@@ -1062,13 +1086,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L6" s="1" t="n">
-        <v>44561</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>2021</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1113,8 +1141,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE6" s="1" t="n">
-        <v>45677</v>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
@@ -1170,17 +1200,25 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L7" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>45580</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2024</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1225,8 +1263,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE7" s="1" t="n">
-        <v>45677</v>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1286,13 +1326,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L8" s="1" t="n">
-        <v>44561</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
-        <v>2021</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1337,8 +1381,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE8" s="1" t="n">
-        <v>45677</v>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
@@ -1390,13 +1436,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L9" s="1" t="n">
-        <v>45625</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
-        <v>2024</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1441,8 +1491,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE9" s="1" t="n">
-        <v>45677</v>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
@@ -1498,8 +1550,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L10" s="1" t="n">
-        <v>45107</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1551,8 +1605,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE10" s="1" t="n">
-        <v>45677</v>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
@@ -1608,8 +1664,10 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L11" s="1" t="n">
-        <v>45838</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1661,8 +1719,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE11" s="1" t="n">
-        <v>45677</v>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -1722,13 +1782,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L12" s="1" t="n">
-        <v>46022</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>2025</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1773,8 +1837,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE12" s="1" t="n">
-        <v>45677</v>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
@@ -1830,13 +1896,17 @@
           <t>people</t>
         </is>
       </c>
-      <c r="L13" s="1" t="n">
-        <v>45519</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>2024</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1881,8 +1951,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE13" s="1" t="n">
-        <v>45677</v>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
@@ -1934,13 +2006,17 @@
           <t>people</t>
         </is>
       </c>
-      <c r="L14" s="1" t="n">
-        <v>45716</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>2025</v>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1981,8 +2057,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE14" s="1" t="n">
-        <v>45677</v>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2038,13 +2116,17 @@
           <t>people</t>
         </is>
       </c>
-      <c r="L15" s="1" t="n">
-        <v>45792</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>2025</v>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2089,8 +2171,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE15" s="1" t="n">
-        <v>45677</v>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
@@ -2142,14 +2226,20 @@
           <t>transactions</t>
         </is>
       </c>
-      <c r="L16" s="1" t="n">
-        <v>45480</v>
-      </c>
-      <c r="M16" s="1" t="n">
-        <v>45115</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>45480</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2023-07-08</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2199,8 +2289,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE16" s="1" t="n">
-        <v>45677</v>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
@@ -2256,14 +2348,20 @@
           <t>transactions</t>
         </is>
       </c>
-      <c r="L17" s="1" t="n">
-        <v>45845</v>
-      </c>
-      <c r="M17" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N17" s="1" t="n">
-        <v>45845</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2313,8 +2411,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE17" s="1" t="n">
-        <v>45677</v>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2374,14 +2474,20 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="L18" s="1" t="n">
-        <v>45845</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N18" s="1" t="n">
-        <v>45845</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2431,8 +2537,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE18" s="1" t="n">
-        <v>45677</v>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -2492,14 +2600,20 @@
           <t>transactions</t>
         </is>
       </c>
-      <c r="L19" s="1" t="n">
-        <v>45845</v>
-      </c>
-      <c r="M19" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N19" s="1" t="n">
-        <v>45845</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2549,8 +2663,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE19" s="1" t="n">
-        <v>45677</v>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
@@ -2606,14 +2722,20 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="L20" s="1" t="n">
-        <v>45845</v>
-      </c>
-      <c r="M20" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N20" s="1" t="n">
-        <v>45845</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2663,8 +2785,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE20" s="1" t="n">
-        <v>45677</v>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
@@ -2716,14 +2840,20 @@
           <t>ratio</t>
         </is>
       </c>
-      <c r="L21" s="1" t="n">
-        <v>45845</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N21" s="1" t="n">
-        <v>45845</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2769,8 +2899,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE21" s="1" t="n">
-        <v>45677</v>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
@@ -2826,14 +2958,20 @@
           <t>users</t>
         </is>
       </c>
-      <c r="L22" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N22" s="1" t="n">
-        <v>45845</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2883,8 +3021,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE22" s="1" t="n">
-        <v>45677</v>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
@@ -2940,14 +3080,20 @@
           <t>ETB</t>
         </is>
       </c>
-      <c r="L23" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>45481</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>45845</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2997,8 +3143,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE23" s="1" t="n">
-        <v>45677</v>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -3054,13 +3202,17 @@
           <t>users</t>
         </is>
       </c>
-      <c r="L24" s="1" t="n">
-        <v>45657</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>2024</v>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3101,8 +3253,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE24" s="1" t="n">
-        <v>45677</v>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -3158,13 +3312,17 @@
           <t>users</t>
         </is>
       </c>
-      <c r="L25" s="1" t="n">
-        <v>45657</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>2024</v>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3205,8 +3363,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE25" s="1" t="n">
-        <v>45677</v>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -3266,13 +3426,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L26" s="1" t="n">
-        <v>45657</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>2024</v>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3313,8 +3477,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE26" s="1" t="n">
-        <v>45677</v>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
@@ -3370,13 +3536,17 @@
           <t>% of GNI</t>
         </is>
       </c>
-      <c r="L27" s="1" t="n">
-        <v>45657</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="n">
-        <v>2024</v>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3421,8 +3591,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE27" s="1" t="n">
-        <v>45677</v>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
@@ -3478,13 +3650,17 @@
           <t>pp</t>
         </is>
       </c>
-      <c r="L28" s="1" t="n">
-        <v>44561</v>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2021-12-31</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>2021</v>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3529,8 +3705,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE28" s="1" t="n">
-        <v>45677</v>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
@@ -3586,13 +3764,17 @@
           <t>pp</t>
         </is>
       </c>
-      <c r="L29" s="1" t="n">
-        <v>45625</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>2024</v>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3637,8 +3819,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE29" s="1" t="n">
-        <v>45677</v>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
@@ -3694,13 +3878,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L30" s="1" t="n">
-        <v>45657</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>2024</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3745,8 +3933,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE30" s="1" t="n">
-        <v>45677</v>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -3806,13 +3996,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L31" s="1" t="n">
-        <v>45657</v>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="n">
-        <v>2024</v>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3857,8 +4051,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE31" s="1" t="n">
-        <v>45677</v>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
@@ -3914,13 +4110,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L32" s="1" t="n">
-        <v>46022</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="n">
-        <v>2025</v>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3965,8 +4165,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE32" s="1" t="n">
-        <v>45677</v>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
@@ -4022,13 +4224,17 @@
           <t>people</t>
         </is>
       </c>
-      <c r="L33" s="1" t="n">
-        <v>47118</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2028-12-31</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>2028</v>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -4073,8 +4279,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE33" s="1" t="n">
-        <v>45677</v>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
@@ -4130,13 +4338,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="L34" s="1" t="n">
-        <v>47848</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2030-12-31</t>
+        </is>
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>2030</v>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -4177,8 +4389,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE34" s="1" t="n">
-        <v>45677</v>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
@@ -4228,13 +4442,17 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" s="1" t="n">
-        <v>44333</v>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2021-05-17</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>2021</v>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4279,8 +4497,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE35" s="1" t="n">
-        <v>45677</v>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
@@ -4330,13 +4550,17 @@
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" s="1" t="n">
-        <v>44774</v>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>2022</v>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4377,8 +4601,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE36" s="1" t="n">
-        <v>45677</v>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
@@ -4428,13 +4654,17 @@
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" s="1" t="n">
-        <v>45139</v>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>2023</v>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4475,8 +4705,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE37" s="1" t="n">
-        <v>45677</v>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
@@ -4526,13 +4758,17 @@
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" s="1" t="n">
-        <v>45292</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="n">
-        <v>2024</v>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -4577,8 +4813,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE38" s="1" t="n">
-        <v>45677</v>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
@@ -4628,13 +4866,17 @@
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" s="1" t="n">
-        <v>45502</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="n">
-        <v>2024</v>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -4675,8 +4917,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE39" s="1" t="n">
-        <v>45677</v>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
@@ -4726,8 +4970,10 @@
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" s="1" t="n">
-        <v>45566</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -4779,8 +5025,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE40" s="1" t="n">
-        <v>45677</v>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
@@ -4830,8 +5078,10 @@
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" s="1" t="n">
-        <v>45957</v>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -4879,8 +5129,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE41" s="1" t="n">
-        <v>45677</v>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
@@ -4930,8 +5182,10 @@
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" s="1" t="n">
-        <v>46009</v>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -4979,8 +5233,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE42" s="1" t="n">
-        <v>45677</v>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
@@ -5030,17 +5286,25 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="M43" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="N43" s="1" t="n">
-        <v>45838</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2021</v>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -5085,8 +5349,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE43" s="1" t="n">
-        <v>45677</v>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
@@ -5136,13 +5402,17 @@
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" s="1" t="n">
-        <v>46006</v>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="n">
-        <v>2025</v>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -5183,8 +5453,10 @@
           <t>Example_Trainee</t>
         </is>
       </c>
-      <c r="AE44" s="1" t="n">
-        <v>45677</v>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
       </c>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
